--- a/out/Attention-Mamba1_repeat_5_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>-0.0002483216076134704</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>2.862781312624584</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>5.729988120071376</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0.4292868280531326</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>3.721938111162561</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0.5367482159670116</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>4.366215956988445</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0.7694260221130821</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>5.368622908209594</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0.823133783979807</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>6.245521495751684</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0.8723559007203067</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>7.167161799737418</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0.3936779932442424</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>7.081436961217965</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0.1901278339150219</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>7.067707225764527</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0.09059086529011458</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>7.058608847224108</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0.02684144147180984</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>7.021604368489845</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0.0177546126023494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>7.03025813720317</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0.009084777374864902</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>7.030662109637737</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0.004644772412928876</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>7.030861469843334</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0.001742647273775515</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>7.029699226626787</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0.0009478819037336858</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>7.029850612288447</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0.0004535591814721555</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>7.029810041433628</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0.0002793630289387267</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>7.029914198781421</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0.0001432291586779051</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>7.029922158848039</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>6.69347054165328e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>7.029912675989066</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>4.104926959945762e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>7.029928088545028</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>7.02991885720801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>7.029911254225207</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>7.029907081053616</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>7.029901358774585</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>7.029896289419217</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>7.029891924445248</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>7.029893015691704</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>7.029892326084568</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>7.02989235639697</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>7.02989216694446</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>7.029892219991163</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>7.029892273037865</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>7.029892235147363</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>7.029892106319656</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>7.02989196233575</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>7.029891856242344</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>7.029891621321232</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>7.02989178803944</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>7.029891985070051</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>7.029891825929942</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>7.029891863820444</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>7.029892060851054</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>7.029892038116753</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>7.029891886554745</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>7.029891810773742</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>7.029891909289047</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>7.029891916867147</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>7.029892182100661</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>7.029891886554745</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>7.029892129053958</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>7.029892212413063</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>7.029892045694854</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>7.029892235147363</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>7.029891886554745</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>7.029891681946035</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>7.02989179561754</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>7.029891810773742</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>7.02989157585263</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>7.029891636477433</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>7.029891507649725</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>7.029891644055533</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>7.029891818351842</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>7.02989196233575</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>7.02989179561754</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>7.02989178803944</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>7.029891500071625</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>7.029891515227827</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>7.029891742570838</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>7.029891727414637</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>7.029891833508042</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>7.029891560696429</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>7.029891659211733</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>7.029891810773742</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>7.029891825929942</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>7.029891886554745</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>7.029891985070051</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>7.029891818351842</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>7.029891772883239</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>7.029891757727039</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>7.02989179561754</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>7.029891810773742</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>7.029891803195642</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.857095742388521e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.007895410060882568</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.008146695792675018</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.007640302181243896</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01224344968795776</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.009864598512649536</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.008802823722362518</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.007851503789424896</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00795610249042511</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.008135028183460236</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.008061408996582031</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.00780901312828064</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.007523812353610992</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.008287191390991211</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.007966130971908569</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.008561909198760986</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.008087784051895142</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.00816623866558075</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.007674761116504669</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.008291549980640411</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.008577160537242889</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.009358353912830353</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01129961013793945</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.009604178369045258</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008952178061008453</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008596122264862061</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.008260481059551239</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.007887512445449829</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0091509148478508</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.008898310363292694</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008678480982780457</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.008323542773723602</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.008143804967403412</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.008526965975761414</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.008628971874713898</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01080360263586044</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02017010748386383</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0144524872303009</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01380341872572899</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01301725953817368</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>0</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01275688037276268</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>0</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01162384450435638</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>0</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01590418443083763</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01893522217869759</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02301893010735512</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.02624040096998215</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01139789819717407</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01795225962996483</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01176392287015915</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01345080882310867</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01048333197832108</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01210751384496689</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01187680661678314</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01094309240579605</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01064296066761017</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01139609515666962</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.008252896368503571</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02797828242182732</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01547820493578911</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01068006455898285</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01030248403549194</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01092655956745148</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01107370108366013</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01331175491213799</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02364629879593849</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.05617338046431541</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01300330087542534</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01184137165546417</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01155263185501099</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01214710623025894</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.009754635393619537</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.009231381118297577</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009926497936248779</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01008148491382599</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.009855620563030243</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.009895317256450653</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0084524005651474</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.009105369448661804</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01094319671392441</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01171950995922089</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.009519927203655243</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.008346788585186005</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0107124000787735</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01259348541498184</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01000030338764191</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.008707992732524872</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.008963435888290405</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009350724518299103</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01194166392087936</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01070912927389145</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.009446889162063599</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01157475262880325</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.008969001471996307</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01676196977496147</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01096262037754059</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01010791212320328</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.008440688252449036</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.008263148367404938</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.009189143776893616</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.009251855313777924</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.007991015911102295</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.007820971310138702</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01249334961175919</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009216628968715668</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.008250914514064789</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.009033896028995514</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.008943326771259308</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.007926717400550842</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.007994309067726135</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.007851265370845795</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.009094946086406708</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007416993379592896</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.00756409764289856</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.008118771016597748</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.008158415555953979</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.008019454777240753</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.008327394723892212</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.009060762822628021</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007728040218353271</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007466211915016174</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.007770933210849762</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.008080363273620605</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.008220888674259186</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.007848992943763733</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.008458591997623444</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.009812146425247192</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.007895410060882568</v>
+        <v>0.007895432412624359</v>
       </c>
       <c r="JB2" t="n">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.008146695792675018</v>
+        <v>0.008146710693836212</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.01224344968795776</v>
+        <v>0.01224344223737717</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.009864598512649536</v>
+        <v>0.009864643216133118</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.008802823722362518</v>
+        <v>0.008802816271781921</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.007851503789424896</v>
+        <v>0.007851541042327881</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.00795610249042511</v>
+        <v>0.007956109941005707</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.008135028183460236</v>
+        <v>0.008135035634040833</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.008061408996582031</v>
+        <v>0.008061401546001434</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.00780901312828064</v>
+        <v>0.007809005677700043</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.007523812353610992</v>
+        <v>0.007523804903030396</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.008561909198760986</v>
+        <v>0.008561894297599792</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.008087784051895142</v>
+        <v>0.008087776601314545</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.00816623866558075</v>
+        <v>0.008166223764419556</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.008291549980640411</v>
+        <v>0.008291557431221008</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.008577160537242889</v>
+        <v>0.008577138185501099</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.009358353912830353</v>
+        <v>0.009358331561088562</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.01129961013793945</v>
+        <v>0.01129960268735886</v>
       </c>
       <c r="JB23" t="n">
         <v>0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.009604178369045258</v>
+        <v>0.009604185819625854</v>
       </c>
       <c r="JB24" t="n">
         <v>0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.008952178061008453</v>
+        <v>0.00895216315984726</v>
       </c>
       <c r="JB25" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.007887512445449829</v>
+        <v>0.00788753479719162</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0091509148478508</v>
+        <v>0.009150899946689606</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.008678480982780457</v>
+        <v>0.00867847353219986</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.008323542773723602</v>
+        <v>0.008323535323143005</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.008143804967403412</v>
+        <v>0.008143827319145203</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.008526965975761414</v>
+        <v>0.00852695107460022</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.008628971874713898</v>
+        <v>0.008628979325294495</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.01080360263586044</v>
+        <v>0.01080362498760223</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.02017010748386383</v>
+        <v>0.02017007768154144</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0144524872303009</v>
+        <v>0.0144524835050106</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.01380341872572899</v>
+        <v>0.01380342245101929</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.01275688037276268</v>
+        <v>0.01275686174631119</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01162384450435638</v>
+        <v>0.011623814702034</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01590418443083763</v>
+        <v>0.01590420305728912</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01893522217869759</v>
+        <v>0.01893521100282669</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.02301893010735512</v>
+        <v>0.02301895245909691</v>
       </c>
       <c r="JB45" t="n">
         <v>0.2599999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02624040096998215</v>
+        <v>0.02624039724469185</v>
       </c>
       <c r="JB46" t="n">
         <v>0.2599999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01139789819717407</v>
+        <v>0.01139788329601288</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.02000000000000007</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01795225962996483</v>
+        <v>0.01795227453112602</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01345080882310867</v>
+        <v>0.01345080137252808</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.01048333197832108</v>
+        <v>0.01048332452774048</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.01210751384496689</v>
+        <v>0.01210752129554749</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.8599999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01187680661678314</v>
+        <v>0.01187679171562195</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.01094309240579605</v>
+        <v>0.01094310730695724</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.01064296066761017</v>
+        <v>0.01064293086528778</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.01139609515666962</v>
+        <v>0.011396124958992</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.008252896368503571</v>
+        <v>0.008252918720245361</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.02797828242182732</v>
+        <v>0.02797827124595642</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.01547820493578911</v>
+        <v>0.01547820121049881</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.01068006455898285</v>
+        <v>0.01068004220724106</v>
       </c>
       <c r="JB60" t="n">
         <v>0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.01030248403549194</v>
+        <v>0.01030246913433075</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01092655956745148</v>
+        <v>0.01092655211687088</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.01331175491213799</v>
+        <v>0.01331175118684769</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.02364629879593849</v>
+        <v>0.0236462838947773</v>
       </c>
       <c r="JB65" t="n">
         <v>0.1600000000000001</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.05617338046431541</v>
+        <v>0.05617336183786392</v>
       </c>
       <c r="JB66" t="n">
         <v>0.1600000000000001</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.01300330087542534</v>
+        <v>0.01300333812832832</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01184137165546417</v>
+        <v>0.01184135675430298</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.01155263185501099</v>
+        <v>0.01155266165733337</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01214710623025894</v>
+        <v>0.01214713603258133</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.009754635393619537</v>
+        <v>0.009754613041877747</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.009231381118297577</v>
+        <v>0.009231358766555786</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.009926497936248779</v>
+        <v>0.009926505386829376</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.01008148491382599</v>
+        <v>0.01008149236440659</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.009855620563030243</v>
+        <v>0.009855605661869049</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.0084524005651474</v>
+        <v>0.008452422916889191</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.009105369448661804</v>
+        <v>0.00910535454750061</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.01094319671392441</v>
+        <v>0.0109432116150856</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.01171950995922089</v>
+        <v>0.01171954721212387</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.009519927203655243</v>
+        <v>0.009519942104816437</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.008346788585186005</v>
+        <v>0.008346781134605408</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>4.989783636080341</v>
@@ -66929,7 +66929,7 @@
         <v>0.0107124000787735</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>4.989783673970843</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.01259348541498184</v>
+        <v>0.01259347423911095</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>4.989783871001453</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.01000030338764191</v>
+        <v>0.0100003182888031</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>4.989783848267152</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.008707992732524872</v>
+        <v>0.008707985281944275</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>4.989783696705144</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.008963435888290405</v>
+        <v>0.008963450789451599</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>4.989783620924141</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.009350724518299103</v>
+        <v>0.009350717067718506</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>4.989783719439446</v>
@@ -71699,7 +71699,7 @@
         <v>0.01194166392087936</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>4.989783727017546</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01070912927389145</v>
+        <v>0.01070909947156906</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>4.98978399225106</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.009446889162063599</v>
+        <v>0.009446904063224792</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>4.989783696705144</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.01157475262880325</v>
+        <v>0.01157476007938385</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.989783939204357</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.008969001471996307</v>
+        <v>0.008969008922576904</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>4.989784022563462</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.01676196977496147</v>
+        <v>0.01676196232438087</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>4.989783855845253</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.01096262037754059</v>
+        <v>0.01096262782812119</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>4.989784045297762</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.01010791212320328</v>
+        <v>0.01010792702436447</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>4.989783696705144</v>
@@ -78059,7 +78059,7 @@
         <v>0.008440688252449036</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>4.989783492096433</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.008263148367404938</v>
+        <v>0.00826311856508255</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.007991015911102295</v>
+        <v>0.007990993559360504</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.007820971310138702</v>
+        <v>0.007820993661880493</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>4.989783317800124</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.009216628968715668</v>
+        <v>0.009216651320457458</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.008250914514064789</v>
+        <v>0.008250921964645386</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.1199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.008943326771259308</v>
+        <v>0.008943334221839905</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.007926717400550842</v>
+        <v>0.007926739752292633</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.007994309067726135</v>
+        <v>0.007994323968887329</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.007851265370845795</v>
+        <v>0.007851287722587585</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.009094946086406708</v>
+        <v>0.009094953536987305</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.007416993379592896</v>
+        <v>0.007417000830173492</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.00756409764289856</v>
+        <v>0.007564090192317963</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.008158415555953979</v>
+        <v>0.008158393204212189</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.008019454777240753</v>
+        <v>0.008019469678401947</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.2599999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.008327394723892212</v>
+        <v>0.008327387273311615</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.2599999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.009060762822628021</v>
+        <v>0.009060733020305634</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.2599999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.007466211915016174</v>
+        <v>0.007466234266757965</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.2599999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.007770933210849762</v>
+        <v>0.007770910859107971</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3999999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.008080363273620605</v>
+        <v>0.008080355823040009</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.008220888674259186</v>
+        <v>0.008220881223678589</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.007848992943763733</v>
+        <v>0.007848985493183136</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.008458591997623444</v>
+        <v>0.00845857709646225</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3700000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.009812146425247192</v>
+        <v>0.009812138974666595</v>
       </c>
       <c r="JB126" t="n">
         <v>0.7200000000000004</v>
